--- a/important_mails_2026-06-28.xlsx
+++ b/important_mails_2026-06-28.xlsx
@@ -1204,7 +1204,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>店铺绩效类</t>
+          <t>付款/资金类</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1219,74 +1219,21 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Sun, 21 Jun 2026 14:27:31 +0000</t>
+          <t>Fri, 26 Jun 2026 14:38:10 +0000</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Automated unfulfillable FBA inventory removal notification</t>
+          <t>Tu pago está en camino</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>96
- Hello Weihai US,
-The following automated unfulfillable FBA removal orders have been created based on your automated settings.
- Removal order ID 1M28ecQsao
- You can view the removals on Removal Order Details in your seller account by using the Search tool.
-The next removal order will be created as scheduled on June 22, 2026 in accordance with your settings if you have unfulfillable inventory at that time.
-To make changes to the shipping address, frequency of your automated unfulfillable removals, or other settings, go to Automated unfulfillable removal settings in your seller account.
- Thank you.
-The Fulfillment by Amazon team
-Please note: This email was sent from a notification-only address that cannot accept incoming email. Please do not reply to this email.
- Report an issue with this email
- If you have any questions visit: Seller Central
- To change your email preferences visit: Notification Preferences
- Copyright 2026 Amazon, Inc, or its affiliates. All rights reserved.
- Amazon.com, 410 Terry Avenue North, Seattle, WA 98109-5210
- SPC-USAmazon-492583430909528</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 26 Jun 2026 14:38:10 +0000</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Tu pago está en camino</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1303,39 +1250,39 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Fri, 26 Jun 2026 14:37:54 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1355,39 +1302,39 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Thu, 25 Jun 2026 13:52:57 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1404,39 +1351,39 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Thu, 25 Jun 2026 13:51:45 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1456,39 +1403,39 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Thu, 25 Jun 2026 13:45:52 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1508,39 +1455,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Thu, 25 Jun 2026 01:48:12 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Updated China tax report link for October - December 2025</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>96
  We’re resending your quarterly tax report which includes data such as identity information, number of transactions, revenue, and commission and service fees.
@@ -1558,39 +1505,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Tue, 23 Jun 2026 16:59:05 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Download your China tax report for October - December 2025</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>96
  You can now download your quarterly tax report which includes data such as identity information, number of transactions, revenue, and commission and service fees.
@@ -1606,39 +1553,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Tue, 23 Jun 2026 14:09:38 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1658,39 +1605,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Tue, 23 Jun 2026 14:09:19 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1707,39 +1654,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Mon, 22 Jun 2026 16:37:09 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;informacion-vendedor@amazon.mx&gt;</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Pago del saldo en tu cuenta de pagos de Vender en Amazon</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>Estimado vendedor:
  Hemos realizado un cargo en tu tarjeta de crédito (Visa) por valor de MXN 192.85 con el fin de saldar tu cuenta de vendedor de Amazon.
@@ -1751,39 +1698,39 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Mon, 22 Jun 2026 14:05:42 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1803,39 +1750,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Mon, 22 Jun 2026 12:44:57 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1852,92 +1799,40 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>Sun, 21 Jun 2026 12:50:33 +0000</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>Your payment is on the way</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- Congratulations! Your payment is on the way and will arrive soon.
- Disbursement attempted
-Congratulations Weihai CA! Your payment is on the way and will arrive within three to five days.
-On 06/21/26 12:50 EDT, we initiated a transfer to your payment method (bank account ending in 151) in the amount of CAD
- 304.60.
- If the amount is less than expected, here are a few questions to consider:
- Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
- Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
-To learn more about Payment Reports in Seller Central, please visit our official course.
-We wish you continued success!
-Thank you for selling in the Amazon Store,
-Amazon Services
-Help us improve your payment experience on Amaz</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Wed, 24 Jun 2026 04:08:32 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>"seller.service05@amazon.com" &lt;seller.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>[Case ID 20858098381] *UPDATE* US - Food and Product Safety - ASIN:
  B0DD7R3PPG</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>96
 [Case ID 20858098381] *UPDATE* US - Food and Product Safety - ASIN: B0DD7R3PPG
@@ -1949,40 +1844,40 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Tue, 23 Jun 2026 02:52:15 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC - DOC REVIEW
@@ -2001,39 +1896,39 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Fri, 26 Jun 2026 14:40:10 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2048,39 +1943,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Fri, 26 Jun 2026 14:07:09 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Luana Camargo, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -2108,39 +2003,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Thu, 25 Jun 2026 22:31:41 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Tus límites de capacidad de Logística de Amazon para julio</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>96
  Tus límites de capacidad de Logística de Amazon para julio
@@ -2169,39 +2064,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Thu, 25 Jun 2026 01:48:42 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Zespół Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Łącze do zaktualizowanego raportu podatkowego dotyczącego Chin za okres od października do grudnia 2025 r.</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>96
  Ponownie przesyłamy kwartalny raport podatkowy, który obejmuje dane takie jak informacje o tożsamości, liczba transakcji, przychody oraz prowizje i opłaty za usługi.
@@ -2219,39 +2114,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Wed, 24 Jun 2026 10:01:00 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2270,39 +2165,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Tue, 23 Jun 2026 16:59:26 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Zespół Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Pobierz raport podatkowy dla Chin za okres od października do grudnia 2025 r.</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>96
  Możesz teraz pobrać kwartalny raport podatkowy, który zawiera dane, takie jak informacje identyfikacyjne, liczba transakcji, przychody oraz prowizje i opłaty za usługi.
@@ -2316,39 +2211,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Tue, 23 Jun 2026 00:26:49 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>&lt;p&gt;Grazie per aver creato un nuovo caso: -- 12908112692&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>96
 &lt;p&gt;Grazie per aver creato un nuovo caso: -- 12908112692&lt;/p&gt;
@@ -2363,39 +2258,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Mon, 22 Jun 2026 09:29:52 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Prime会员日明天开始：最后提报促销活动的机会</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩
 尊敬的卖家，
@@ -2419,86 +2314,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>货件/库存类</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>Sun, 21 Jun 2026 12:49:43 +0000</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>Pagamento elaborato con successo</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
-This title will display on mobile devices
- Congratulazioni. Il pagamento è stato elaborato con successo e ti sarà accreditato a breve.
- Tentativo di pagamento
-Congratulazioni Weihai EU! Il pagamento è stato elaborato con successo e ti sarà accreditato nel giro di da tre a cinque giorni.
-In data 06/21/26 12:49 CEST, abbiamo avviato un trasferimento sul tuo metodo di pagamento (conto bancario che termina con 229) dell’importo di €
- 204,78.
- Se l’importo è inferiore a quanto atteso, tieni in considerazione le seguenti domande:
- Hai un saldo non disponibile? Amazon potrebbe trattenere una certa somma per coprire i costi di eventuali resi, reclami o contestazioni di una transazione (chargeback) da parte degli acquirenti. In questo caso, il saldo finale nel tuo report sui pagamenti mostrerà il saldo non disponibile corrispondente alla cifra trattenuta.
- Le tue vendite coprono tutte le commissioni e i resi per questo ciclo di fatturazione? L’importo del pagamento rispecchia le attività di vendita, le commissioni di vendita e le tariffe per promozioni o servizi. Ti consigliamo di rivedere il report sui pagamenti nella scheda Report di Seller Central per comprendere le diverse spese che </t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Sat, 27 Jun 2026 04:46:44 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -2522,39 +2370,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Sat, 27 Jun 2026 04:45:39 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -2578,39 +2426,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Sat, 27 Jun 2026 03:25:54 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-07-09</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -2632,39 +2480,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Thu, 25 Jun 2026 12:14:25 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Connect with an Amazon expert at Seller Café—Save $100 with early-bird pricing</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/-ld-EM/7z46y96/6733799304/h/qLPgz01lmZlp6bu7C295K13RXyMwFkd7KKOkI6IliSc)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/4uHYwMZ-ld-EM/7z46y99/6733799304/h/qLPgz01lmZlp6bu7C295K13RXyMwFkd7KKOkI6IliSc)
@@ -2680,39 +2528,92 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 21 Jun 2026 14:27:31 +0000</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Automated unfulfillable FBA inventory removal notification</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Hello Weihai US,
+The following automated unfulfillable FBA removal orders have been created based on your automated settings.
+ Removal order ID 1M28ecQsao
+ You can view the removals on Removal Order Details in your seller account by using the Search tool.
+The next removal order will be created as scheduled on June 22, 2026 in accordance with your settings if you have unfulfillable inventory at that time.
+To make changes to the shipping address, frequency of your automated unfulfillable removals, or other settings, go to Automated unfulfillable removal settings in your seller account.
+ Thank you.
+The Fulfillment by Amazon team
+Please note: This email was sent from a notification-only address that cannot accept incoming email. Please do not reply to this email.
+ Report an issue with this email
+ If you have any questions visit: Seller Central
+ To change your email preferences visit: Notification Preferences
+ Copyright 2026 Amazon, Inc, or its affiliates. All rights reserved.
+ Amazon.com, 410 Terry Avenue North, Seattle, WA 98109-5210
+ SPC-USAmazon-492583430909528</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Sat, 20 Jun 2026 15:35:08 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (hCxOB8pPpU)</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2737,39 +2638,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Sat, 20 Jun 2026 15:10:33 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -2790,39 +2691,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Sat, 20 Jun 2026 04:41:46 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2838,39 +2739,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Fri, 19 Jun 2026 14:16:06 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -2891,39 +2792,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Fri, 19 Jun 2026 08:10:33 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>Amazon Multchannel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF
 Dear Weihai US,
@@ -2937,39 +2838,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Thu, 18 Jun 2026 20:47:57 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (oWLDk2Qx2d)</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2994,39 +2895,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Thu, 18 Jun 2026 20:39:11 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (Emm3dPMsXA)</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3051,39 +2952,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Wed, 17 Jun 2026 17:59:35 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Amazon Multichannel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF
 Dear Weihai EU,
@@ -3097,39 +2998,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Wed, 17 Jun 2026 15:48:24 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3150,39 +3051,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Mon, 15 Jun 2026 16:22:55 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3203,39 +3104,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Sun, 14 Jun 2026 15:05:28 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3256,39 +3157,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Sun, 14 Jun 2026 14:33:45 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $94.16 in an attempt to settle your Amazon seller account balance.
@@ -3304,39 +3205,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 21:11:17 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3357,39 +3258,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 03:06:46 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3405,39 +3306,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 16:09:43 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (JKfyD/ypoS)</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3457,39 +3358,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 04:19:55 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (wrlLFrQcT3)</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3509,39 +3410,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Tue, 9 Jun 2026 18:59:47 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (2605311NRC)</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3561,39 +3462,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Tue, 9 Jun 2026 16:46:32 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3614,39 +3515,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 03:33:45 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3662,39 +3563,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Wed, 3 Jun 2026 05:07:33 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (MtDohxu3JK)</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3714,39 +3615,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Tue, 2 Jun 2026 13:57:10 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (okvedC6bat)</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3766,39 +3667,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Tue, 2 Jun 2026 08:40:44 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3814,39 +3715,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Mon, 1 Jun 2026 19:29:32 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (260520getf)</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3871,39 +3772,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Sun, 31 May 2026 14:43:35 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $143.78 in an attempt to settle your Amazon seller account balance.
@@ -3919,39 +3820,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 01:13:32 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (Xq5h330940)</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3976,39 +3877,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 06:55:02 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (7kDrHSJf1h)</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -4028,39 +3929,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 03:26:42 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4076,39 +3977,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Thu, 18 Jun 2026 14:32:29 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Seller News: June 2026</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -4125,39 +4026,91 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 21 Jun 2026 12:50:33 +0000</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>Your payment is on the way</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ Congratulations! Your payment is on the way and will arrive soon.
+ Disbursement attempted
+Congratulations Weihai CA! Your payment is on the way and will arrive within three to five days.
+On 06/21/26 12:50 EDT, we initiated a transfer to your payment method (bank account ending in 151) in the amount of CAD
+ 304.60.
+ If the amount is less than expected, here are a few questions to consider:
+ Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
+ Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
+To learn more about Payment Reports in Seller Central, please visit our official course.
+We wish you continued success!
+Thank you for selling in the Amazon Store,
+Amazon Services
+Help us improve your payment experience on Amaz</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Sat, 20 Jun 2026 13:23:55 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4174,39 +4127,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Fri, 19 Jun 2026 13:11:15 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4226,39 +4179,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Fri, 19 Jun 2026 13:09:47 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4275,39 +4228,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Thu, 18 Jun 2026 17:21:56 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Download your China tax report for January–March 2026</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>96
  You can now download your quarterly tax report, which includes data such as identity information, number of transactions, revenue, and commission and service fees.
@@ -4324,39 +4277,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Thu, 18 Jun 2026 16:54:51 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Download your China tax report for January - March 2026</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>96
  You can now download your quarterly tax report which includes data such as identity information, number of transactions, revenue, and commission and service fees.
@@ -4373,39 +4326,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Thu, 18 Jun 2026 08:40:50 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Envía el número de registro de España para la responsabilidad ampliada del productor con respecto a los RAEE a más tardar el 30 de septiembre</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Presenta el número de registro de la responsabilidad ampliada del productor a más tardar el 30 de septiembre o se te inscribirá automáticamente en RAP: Pago en mi nombre.
  96
@@ -4414,39 +4367,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Wed, 17 Jun 2026 14:39:03 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4466,39 +4419,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 14:27:04 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4518,39 +4471,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 14:25:49 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4567,39 +4520,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 14:24:48 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4619,39 +4572,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 06:40:46 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>Seller Central &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>重要信息：即刻重新验证您的所有 付款账户或存款方式</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>96
  亲爱的卖家，
@@ -4685,39 +4638,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Mon, 15 Jun 2026 14:24:03 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4737,39 +4690,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Mon, 15 Jun 2026 14:23:28 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4786,39 +4739,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Sun, 14 Jun 2026 13:35:44 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4838,39 +4791,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Sat, 13 Jun 2026 13:28:40 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4890,39 +4843,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Sat, 13 Jun 2026 13:24:36 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4939,39 +4892,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Sat, 13 Jun 2026 13:24:04 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4991,39 +4944,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 23:31:42 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5043,39 +4996,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 12:54:19 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5095,39 +5048,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Thu, 11 Jun 2026 15:13:12 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.pl&gt;</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>Nieuregulowane saldo na koncie Amazon</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>Witamy!
  Masz na swoim koncie nieuregulowane saldo w wysokośc PLN 42.71. Obciążymy tą kwotą kartę kredytową zarejestrowaną jako metoda płatności dla Twojego konta
@@ -5141,39 +5094,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Thu, 11 Jun 2026 11:53:43 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5193,39 +5146,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Thu, 11 Jun 2026 11:51:09 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5242,39 +5195,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 16:29:28 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;informacion-vendedor@amazon.mx&gt;</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>Pago del saldo en tu cuenta de pagos de Vender en Amazon</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>Estimado vendedor:
  Hemos realizado un cargo en tu tarjeta de crédito (Visa) por valor de MXN 90.75 con el fin de saldar tu cuenta de vendedor de Amazon.
@@ -5286,39 +5239,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 02:57:49 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5338,39 +5291,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 02:56:47 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5387,39 +5340,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 02:56:35 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5439,39 +5392,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Mon, 8 Jun 2026 14:05:53 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5491,39 +5444,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Sun, 7 Jun 2026 13:51:46 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5543,39 +5496,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 13:21:50 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5595,39 +5548,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 13:21:46 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5644,39 +5597,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 15:15:46 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5696,39 +5649,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Wed, 3 Jun 2026 14:55:10 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5745,39 +5698,39 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Mon, 1 Jun 2026 14:58:44 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5797,39 +5750,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Sun, 31 May 2026 14:55:36 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5849,39 +5802,39 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Sun, 31 May 2026 14:55:10 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5901,39 +5854,39 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 14:37:25 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5950,39 +5903,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 23:31:40 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6002,39 +5955,39 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 14:43:44 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6054,39 +6007,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 14:42:27 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6106,39 +6059,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Fri, 19 Jun 2026 12:40:58 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -6154,39 +6107,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Fri, 19 Jun 2026 08:56:40 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Submit missing VAT Registration Information</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -6212,39 +6165,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Fri, 19 Jun 2026 08:39:22 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Submit missing VAT Registration Information</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -6270,39 +6223,39 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Thu, 18 Jun 2026 10:15:17 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Submit EPR registration numbers by June 30</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>96
  You’ll be enrolled in EPR Pay on Behalf unless you provide valid Extended Producer Responsibility registration numbers by June 30
@@ -6311,39 +6264,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Thu, 18 Jun 2026 04:34:37 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号
@@ -6368,40 +6321,40 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Wed, 17 Jun 2026 06:03:25 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC - DOC REVIEW
@@ -6419,40 +6372,40 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 19:23:07 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;seller.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20858098381] US - Food and Product Safety - ASIN:
  B0DD7R3PPG</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 20858098381] US - Food and Product Safety - ASIN: B0DD7R3PPG
@@ -6477,39 +6430,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 11:11:59 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>96
  Hello xiao jianming,
@@ -6528,39 +6481,39 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 11:09:32 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -6579,39 +6532,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 11:09:28 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>96
  Hello xiao jianming,
@@ -6630,39 +6583,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 10:32:14 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>"pars-rp-core-sellerappeals-transfer@amazon.com" &lt;pars-rp-core-sellerappeals-transfer@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20516062511] 危险物品（危险品）</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 20516062511] 危险物品（危险品）
@@ -6690,39 +6643,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 10:13:22 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -6741,39 +6694,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Mon, 15 Jun 2026 20:37:03 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>Important message: your account is at risk of deactivation</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>96
  96
@@ -6793,40 +6746,40 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Mon, 15 Jun 2026 06:46:26 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC - DOC REVIEW
@@ -6842,40 +6795,40 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Sat, 13 Jun 2026 10:18:49 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>"toys-safety-mv@amazon.com" &lt;toys-safety-mv@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20326051091] SELLER: A192R36HNXVJ38, ASIN: B0DRTR7GYJ,
  MARKETPLACE: 1 - PS - APPEAL</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 20326051091] SELLER: A192R36HNXVJ38, ASIN: B0DRTR7GYJ, MARKETPLACE: 1 - PS - APPEAL
@@ -6902,39 +6855,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Sat, 13 Jun 2026 03:03:53 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Review issue on FBA Shipment (FBA1234567)</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>96
  Review shipment defects to avoid reoccurrence
@@ -6954,40 +6907,40 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 13:54:53 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>"toys-safety-mv@amazon.com" &lt;toys-safety-mv@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20326051091] SELLER: A192R36HNXVJ38, ASIN: B0DRTR7GYJ,
  MARKETPLACE: 1 - PS - APPEAL</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 20326051091] SELLER: A192R36HNXVJ38, ASIN: B0DRTR7GYJ, MARKETPLACE: 1 - PS - APPEAL
@@ -7000,40 +6953,40 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 10:51:40 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC - DOC REVIEW
@@ -7052,39 +7005,39 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Thu, 11 Jun 2026 13:08:16 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hello Weihai CA,
@@ -7103,40 +7056,40 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Thu, 11 Jun 2026 04:06:26 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-vendor@amazon.ca" &lt;cscompliance-docreview-vendor@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 7 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 7 - CSC - DOC REVIEW
@@ -7152,39 +7105,39 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 19:04:36 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>New EU restriction on textile and footwear disposal</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>96
  By July 19, update your removal settings for apparel, clothing and footwear in EU fulfillment centers
@@ -7199,39 +7152,39 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 18:11:21 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -7249,40 +7202,40 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 02:29:01 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>"toys-safety-mv@amazon.com" &lt;toys-safety-mv@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20326051091] SELLER: A192R36HNXVJ38, ASIN: B0DRTR7GYJ,
  MARKETPLACE: 1 - PS - APPEAL</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 RE:[CASE 20326051091] SELLER: A192R36HNXVJ38, ASIN: B0DRTR7GYJ, MARKETPLACE: 1 - PS - APPEAL
@@ -7294,39 +7247,39 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Tue, 9 Jun 2026 18:10:54 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -7344,39 +7297,39 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Tue, 9 Jun 2026 15:30:18 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>Your VAT invoice for EPR Pay on Behalf charges for Amazon.es sales</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Tu factura con IVA de los cargos del servicio RAP - Pagamos en tu nombre para las ventas de Amazon.es |
 Your VAT invoice for EPR Pay on Behalf charges for Amazon.es sales
@@ -7389,40 +7342,40 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Mon, 8 Jun 2026 08:56:37 +0000</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC - DOC REVIEW
@@ -7438,40 +7391,40 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Mon, 8 Jun 2026 08:52:27 +0000</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0GKPTF1T7, MARKETPLACE:
  A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A1UYGOR4ZW45MU, ASIN: B0GKPTF1T7, MARKETPLACE: A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review
@@ -7499,39 +7452,39 @@
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Sun, 7 Jun 2026 17:51:49 +0000</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -7550,39 +7503,39 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Fri, 5 Jun 2026 19:25:12 +0000</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -7600,39 +7553,39 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Fri, 5 Jun 2026 03:06:03 +0000</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 You recently received a notice about the removal of your listing(s) for the product(s) listed below.
@@ -7652,39 +7605,39 @@
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 19:23:36 +0000</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -7702,39 +7655,39 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 19:17:04 +0000</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -7752,39 +7705,39 @@
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 12:40:15 +0000</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -7800,39 +7753,39 @@
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 12:33:38 +0000</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -7851,39 +7804,39 @@
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Wed, 3 Jun 2026 21:10:43 +0000</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -7901,39 +7854,39 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Wed, 3 Jun 2026 19:18:22 +0000</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -7951,39 +7904,39 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Wed, 3 Jun 2026 19:12:35 +0000</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -8001,39 +7954,39 @@
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Wed, 3 Jun 2026 02:36:04 +0000</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>"compliance-ops-mass-programs@amazon.com" &lt;compliance-ops-mass-programs@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12662433092] 通过亚马逊完成奥地利EPR注册</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 12662433092] 通过亚马逊完成奥地利EPR注册
@@ -8068,39 +8021,39 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Tue, 2 Jun 2026 12:53:21 +0000</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -8116,40 +8069,40 @@
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Mon, 1 Jun 2026 10:39:43 +0000</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.se" &lt;cscompliance-docreview-seller@amazon.se&gt;</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE:
  A2NODRKZP88ZB9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr"/>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE: A2NODRKZP88ZB9 - SPO - Seller Partner Outreach - Document Review
@@ -8166,40 +8119,40 @@
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Sun, 31 May 2026 14:31:42 +0000</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>"toys-safety-mv@amazon.com" &lt;toys-safety-mv@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - PS -
  APPEAL</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - PS - APPEAL
@@ -8220,39 +8173,39 @@
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 16:11:48 +0000</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr"/>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -8270,39 +8223,39 @@
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 16:09:04 +0000</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr"/>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -8320,39 +8273,39 @@
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 16:10:43 +0000</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr"/>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -8370,39 +8323,39 @@
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 16:07:21 +0000</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr"/>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -8417,6 +8370,53 @@
  If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfil the compliance requirements.
 -
  If you believe that your products are exempt from these requirements, submit documentation demonstrating why they are not subj</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 21 Jun 2026 12:49:43 +0000</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>Pagamento elaborato con successo</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+This title will display on mobile devices
+ Congratulazioni. Il pagamento è stato elaborato con successo e ti sarà accreditato a breve.
+ Tentativo di pagamento
+Congratulazioni Weihai EU! Il pagamento è stato elaborato con successo e ti sarà accreditato nel giro di da tre a cinque giorni.
+In data 06/21/26 12:49 CEST, abbiamo avviato un trasferimento sul tuo metodo di pagamento (conto bancario che termina con 229) dell’importo di €
+ 204,78.
+ Se l’importo è inferiore a quanto atteso, tieni in considerazione le seguenti domande:
+ Hai un saldo non disponibile? Amazon potrebbe trattenere una certa somma per coprire i costi di eventuali resi, reclami o contestazioni di una transazione (chargeback) da parte degli acquirenti. In questo caso, il saldo finale nel tuo report sui pagamenti mostrerà il saldo non disponibile corrispondente alla cifra trattenuta.
+ Le tue vendite coprono tutte le commissioni e i resi per questo ciclo di fatturazione? L’importo del pagamento rispecchia le attività di vendita, le commissioni di vendita e le tariffe per promozioni o servizi. Ti consigliamo di rivedere il report sui pagamenti nella scheda Report di Seller Central per comprendere le diverse spese che </t>
         </is>
       </c>
     </row>
